--- a/data/corrective_actions.xlsx
+++ b/data/corrective_actions.xlsx
@@ -489,10 +489,10 @@
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45448</v>
+        <v>45478</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>45493</v>
+        <v>45523</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="D3" s="1" t="n">
-        <v>45460</v>
+        <v>45490</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>45517</v>
+        <v>45547</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45461</v>
+        <v>45492</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>45476</v>
+        <v>45507</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -633,10 +633,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45470</v>
+        <v>45501</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>45511</v>
+        <v>45542</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -681,10 +681,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45462</v>
+        <v>45492</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>45522</v>
+        <v>45552</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45465</v>
+        <v>45496</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>45510</v>
+        <v>45541</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45451</v>
+        <v>45481</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>45498</v>
+        <v>45528</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45499</v>
+        <v>45530</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>45516</v>
+        <v>45547</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -873,10 +873,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45501</v>
+        <v>45532</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>45535</v>
+        <v>45566</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -921,10 +921,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45483</v>
+        <v>45514</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>45517</v>
+        <v>45548</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -969,10 +969,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45515</v>
+        <v>45546</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>45565</v>
+        <v>45596</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45513</v>
+        <v>45543</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>45544</v>
+        <v>45574</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1065,10 +1065,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45544</v>
+        <v>45574</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>45603</v>
+        <v>45633</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45548</v>
+        <v>45578</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>45563</v>
+        <v>45593</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45551</v>
+        <v>45582</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>45578</v>
+        <v>45609</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1209,10 +1209,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45554</v>
+        <v>45585</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>45574</v>
+        <v>45605</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1257,10 +1257,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45575</v>
+        <v>45605</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>45629</v>
+        <v>45659</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45618</v>
+        <v>45648</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>45657</v>
+        <v>45687</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45610</v>
+        <v>45640</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>45668</v>
+        <v>45698</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45607</v>
+        <v>45638</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>45651</v>
+        <v>45682</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45659</v>
+        <v>45690</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>45677</v>
+        <v>45708</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1497,10 +1497,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45643</v>
+        <v>45674</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>45694</v>
+        <v>45725</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45650</v>
+        <v>45681</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>45702</v>
+        <v>45733</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45682</v>
+        <v>45711</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>45741</v>
+        <v>45770</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1641,10 +1641,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45681</v>
+        <v>45710</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>45706</v>
+        <v>45735</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45660</v>
+        <v>45691</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>45716</v>
+        <v>45747</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1737,10 +1737,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45659</v>
+        <v>45690</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>45709</v>
+        <v>45740</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45697</v>
+        <v>45726</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>45730</v>
+        <v>45759</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1833,10 +1833,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45693</v>
+        <v>45721</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>45739</v>
+        <v>45767</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1881,10 +1881,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45706</v>
+        <v>45735</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>45739</v>
+        <v>45768</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1929,10 +1929,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45698</v>
+        <v>45727</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>45734</v>
+        <v>45763</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45705</v>
+        <v>45735</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>45749</v>
+        <v>45779</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2025,10 +2025,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45741</v>
+        <v>45771</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>45770</v>
+        <v>45800</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45739</v>
+        <v>45769</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>45796</v>
+        <v>45826</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2121,10 +2121,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45775</v>
+        <v>45806</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>45802</v>
+        <v>45833</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45766</v>
+        <v>45797</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>45814</v>
+        <v>45845</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45776</v>
+        <v>45807</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>45806</v>
+        <v>45837</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45793</v>
+        <v>45824</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>45840</v>
+        <v>45871</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45822</v>
+        <v>45852</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>45848</v>
+        <v>45878</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2361,10 +2361,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45886</v>
+        <v>45917</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>45920</v>
+        <v>45951</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45955</v>
+        <v>45985</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>45983</v>
+        <v>46013</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2457,10 +2457,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45950</v>
+        <v>45980</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>45982</v>
+        <v>46012</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2505,10 +2505,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45945</v>
+        <v>45975</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>45985</v>
+        <v>46015</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2553,10 +2553,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46080</v>
+        <v>46111</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46101</v>
+        <v>46132</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>46061</v>
+        <v>46089</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46118</v>
+        <v>46146</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2649,10 +2649,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>46077</v>
+        <v>46108</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46123</v>
+        <v>46154</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>46088</v>
+        <v>46119</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46121</v>
+        <v>46152</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2745,10 +2745,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>46085</v>
+        <v>46116</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46123</v>
+        <v>46154</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2793,10 +2793,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46100</v>
+        <v>46130</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46127</v>
+        <v>46157</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -2815,12 +2815,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Due Soon</t>
         </is>
       </c>
     </row>
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>46123</v>
+        <v>46154</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46155</v>
+        <v>46186</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>46134</v>
+        <v>46165</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46157</v>
+        <v>46188</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -2911,12 +2911,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Due Soon</t>
         </is>
       </c>
     </row>
@@ -2937,10 +2937,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>46122</v>
+        <v>46152</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46148</v>
+        <v>46178</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -2959,12 +2959,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Due Soon</t>
         </is>
       </c>
     </row>
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>46123</v>
+        <v>46153</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46170</v>
+        <v>46200</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3007,12 +3007,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -3033,10 +3033,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>46130</v>
+        <v>46160</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46189</v>
+        <v>46219</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3081,10 +3081,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46168</v>
+        <v>46198</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46183</v>
+        <v>46213</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3125,28 +3125,28 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Improve signage</t>
+          <t>Update SOP / JSA</t>
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>46028</v>
+        <v>46032</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46087</v>
+        <v>46080</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>E. Asante</t>
+          <t>D. Tetteh</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Mining</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Nkran Open Pit</t>
+          <t>HME Workshop</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -3173,33 +3173,33 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Housekeeping campaign</t>
+          <t>Improve signage</t>
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>46156</v>
+        <v>46146</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46183</v>
+        <v>46194</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>S. Addo</t>
+          <t>F. Agyeman</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Mining</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Water Treatment</t>
+          <t>Explosives Magazine</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -3221,33 +3221,33 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spill kit replenishment</t>
+          <t>Repair edge protection</t>
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>46007</v>
+        <v>46140</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46035</v>
+        <v>46187</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>A. Owusu</t>
+          <t>S. Addo</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Accommodation Camp</t>
+          <t>Fuel Farm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -3269,38 +3269,38 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Repair edge protection</t>
+          <t>Improve signage</t>
         </is>
       </c>
       <c r="D60" s="1" t="n">
-        <v>46135</v>
+        <v>46066</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46184</v>
+        <v>46092</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>S. Addo</t>
+          <t>F. Agyeman</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Tailings Storage Facility</t>
+          <t>Fuel Farm</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3317,33 +3317,33 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Lighting upgrade</t>
+          <t>Housekeeping campaign</t>
         </is>
       </c>
       <c r="D61" s="1" t="n">
-        <v>46161</v>
+        <v>45982</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46234</v>
+        <v>46009</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>D. Tetteh</t>
+          <t>E. Asante</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Power Station</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -3365,18 +3365,18 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spill kit replenishment</t>
+          <t>Housekeeping campaign</t>
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>46020</v>
+        <v>46089</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46063</v>
+        <v>46159</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>D. Tetteh</t>
+          <t>F. Agyeman</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3386,17 +3386,17 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Drill &amp; Blast</t>
+          <t>Explosives Magazine</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -3413,33 +3413,33 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spill kit replenishment</t>
+          <t>Repair edge protection</t>
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>46113</v>
+        <v>46108</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46150</v>
+        <v>46180</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>A. Owusu</t>
+          <t>P. Annan</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Mining</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Esaase Open Pit</t>
+          <t>Power Station</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -3461,38 +3461,38 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Update SOP / JSA</t>
+          <t>Replace fire extinguisher</t>
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>46102</v>
+        <v>46086</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>J. Boateng</t>
+          <t>E. Asante</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Security Gatehouse</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3509,28 +3509,28 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Install machine guard</t>
+          <t>Improve signage</t>
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>46166</v>
+        <v>46086</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46209</v>
+        <v>46157</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>S. Addo</t>
+          <t>A. Owusu</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>Mining</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Elution &amp; Gold Room</t>
+          <t>Nkran Open Pit</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Due Soon</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -3557,28 +3557,28 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Replace fire extinguisher</t>
+          <t>Install machine guard</t>
         </is>
       </c>
       <c r="D66" s="1" t="n">
-        <v>46082</v>
+        <v>46168</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46103</v>
+        <v>46216</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>K. Mensah</t>
+          <t>J. Boateng</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Accommodation Camp</t>
+          <t>Water Treatment</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3605,14 +3605,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Update SOP / JSA</t>
+          <t>Replace fire extinguisher</t>
         </is>
       </c>
       <c r="D67" s="1" t="n">
-        <v>46144</v>
+        <v>46140</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46172</v>
+        <v>46176</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -3621,22 +3621,22 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Mining</t>
+          <t>Processing</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Nkran Open Pit</t>
+          <t>Processing Plant (CIL)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3653,38 +3653,38 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Repair edge protection</t>
+          <t>Update SOP / JSA</t>
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46038</v>
+        <v>46116</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46073</v>
+        <v>46185</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>E. Asante</t>
+          <t>F. Agyeman</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>Mining</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Crushing Circuit</t>
+          <t>Nkran Open Pit</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Due Soon</t>
         </is>
       </c>
     </row>
@@ -3701,33 +3701,33 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Improve signage</t>
+          <t>Replace fire extinguisher</t>
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>46074</v>
+        <v>46007</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46140</v>
+        <v>46057</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>E. Asante</t>
+          <t>J. Boateng</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tailings Storage Facility</t>
+          <t>HME Workshop</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -3749,28 +3749,28 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spill kit replenishment</t>
+          <t>Update SOP / JSA</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
-        <v>46083</v>
+        <v>46037</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46141</v>
+        <v>46109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>E. Asante</t>
+          <t>K. Mensah</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Mining</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Assay Laboratory</t>
+          <t>Haul Roads</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -3797,38 +3797,38 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spill kit replenishment</t>
+          <t>Lighting upgrade</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46008</v>
+        <v>46109</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46045</v>
+        <v>46136</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>F. Agyeman</t>
+          <t>S. Addo</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Processing</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Processing Plant (CIL)</t>
+          <t>Fuel Farm</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -3849,24 +3849,24 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46019</v>
+        <v>46155</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46043</v>
+        <v>46197</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>K. Mensah</t>
+          <t>P. Annan</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Mining</t>
+          <t>Environment</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Drill &amp; Blast</t>
+          <t>Water Treatment</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Due Soon</t>
         </is>
       </c>
     </row>
@@ -3893,28 +3893,28 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lighting upgrade</t>
+          <t>Replace fire extinguisher</t>
         </is>
       </c>
       <c r="D73" s="1" t="n">
-        <v>46076</v>
+        <v>45996</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46145</v>
+        <v>46018</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>J. Boateng</t>
+          <t>A. Owusu</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Mining</t>
+          <t>Logistics</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Nkran Open Pit</t>
+          <t>Warehouse &amp; Stores</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3941,38 +3941,38 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Update SOP / JSA</t>
+          <t>Bund repair at fuel storage</t>
         </is>
       </c>
       <c r="D74" s="1" t="n">
-        <v>46151</v>
+        <v>46115</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46186</v>
+        <v>46139</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>P. Annan</t>
+          <t>M. Quaye</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Mining</t>
+          <t>Processing</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Nkran Open Pit</t>
+          <t>Processing Plant (CIL)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -3989,28 +3989,28 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Repair edge protection</t>
+          <t>Install machine guard</t>
         </is>
       </c>
       <c r="D75" s="1" t="n">
-        <v>46023</v>
+        <v>46143</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46051</v>
+        <v>46193</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>K. Mensah</t>
+          <t>E. Asante</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Mining</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Accommodation Camp</t>
+          <t>Drill &amp; Blast</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Due Soon</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4037,14 +4037,14 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Install machine guard</t>
+          <t>Housekeeping campaign</t>
         </is>
       </c>
       <c r="D76" s="1" t="n">
-        <v>46168</v>
+        <v>46018</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46231</v>
+        <v>46084</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -4053,17 +4053,17 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Laboratory</t>
+          <t>Processing</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Assay Laboratory</t>
+          <t>Processing Plant (CIL)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -4085,38 +4085,38 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Repair edge protection</t>
+          <t>Update SOP / JSA</t>
         </is>
       </c>
       <c r="D77" s="1" t="n">
-        <v>45994</v>
+        <v>46143</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46022</v>
+        <v>46190</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>P. Annan</t>
+          <t>D. Tetteh</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Mining</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Administration</t>
+          <t>Drill &amp; Blast</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4137,34 +4137,34 @@
         </is>
       </c>
       <c r="D78" s="1" t="n">
-        <v>45980</v>
+        <v>46124</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46013</v>
+        <v>46184</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>J. Boateng</t>
+          <t>S. Addo</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Environment</t>
+          <t>Processing</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Water Treatment</t>
+          <t>Crushing Circuit</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -4181,14 +4181,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bund repair at fuel storage</t>
+          <t>Improve signage</t>
         </is>
       </c>
       <c r="D79" s="1" t="n">
-        <v>46026</v>
+        <v>46119</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46060</v>
+        <v>46175</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -4202,17 +4202,17 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Water Treatment</t>
+          <t>Tailings Storage Facility</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -4229,14 +4229,14 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Repair edge protection</t>
+          <t>Install machine guard</t>
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>46002</v>
+        <v>46117</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46037</v>
+        <v>46157</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -4245,12 +4245,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>HME Workshop</t>
+          <t>Administration</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Due Soon</t>
         </is>
       </c>
     </row>
@@ -4277,38 +4277,38 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Housekeeping campaign</t>
+          <t>Update SOP / JSA</t>
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>46055</v>
+        <v>46104</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46094</v>
+        <v>46137</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>E. Asante</t>
+          <t>Y. Darko</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Engineering</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Fuel Farm</t>
+          <t>Security Gatehouse</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Closed</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -4325,18 +4325,18 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Repair edge protection</t>
+          <t>Replace fire extinguisher</t>
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>46036</v>
+        <v>46051</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46089</v>
+        <v>46080</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>E. Asante</t>
+          <t>P. Annan</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4346,17 +4346,17 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Explosives Magazine</t>
+          <t>Haul Roads</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -4377,14 +4377,14 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45989</v>
+        <v>46152</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46014</v>
+        <v>46209</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>P. Annan</t>
+          <t>D. Tetteh</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Processing Plant (CIL)</t>
+          <t>Elution &amp; Gold Room</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -4421,18 +4421,18 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Improve signage</t>
+          <t>Spill kit replenishment</t>
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>46016</v>
+        <v>45997</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46085</v>
+        <v>46029</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>M. Quaye</t>
+          <t>P. Annan</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4442,7 +4442,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Fuel Farm</t>
+          <t>HME Workshop</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4452,7 +4452,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Due Soon</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
